--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.74008574121773</v>
+        <v>7.920263932947881</v>
       </c>
       <c r="D2" t="n">
-        <v>48.26230266227152</v>
+        <v>7.842624182619123</v>
       </c>
       <c r="E2" t="n">
-        <v>13.26773267539505</v>
+        <v>2.156006559751696</v>
       </c>
       <c r="F2" t="n">
-        <v>13.04498339295627</v>
+        <v>2.119809801355395</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.99889469008387</v>
+        <v>5.84982038713863</v>
       </c>
       <c r="D3" t="n">
-        <v>35.47714904297171</v>
+        <v>5.765036719482903</v>
       </c>
       <c r="E3" t="n">
-        <v>13.26773267539505</v>
+        <v>2.156006559751696</v>
       </c>
       <c r="F3" t="n">
-        <v>13.04498339295627</v>
+        <v>2.119809801355395</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.96374470178731</v>
+        <v>1.944108514040438</v>
       </c>
       <c r="D4" t="n">
-        <v>12.00842453243508</v>
+        <v>1.9513689865207</v>
       </c>
       <c r="E4" t="n">
-        <v>13.26773267539505</v>
+        <v>2.156006559751696</v>
       </c>
       <c r="F4" t="n">
-        <v>13.04498339295627</v>
+        <v>2.119809801355395</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.2627385718351</v>
+        <v>4.755195017923204</v>
       </c>
       <c r="D5" t="n">
-        <v>29.46880729560358</v>
+        <v>4.788681185535581</v>
       </c>
       <c r="E5" t="n">
-        <v>13.26773267539505</v>
+        <v>2.156006559751696</v>
       </c>
       <c r="F5" t="n">
-        <v>13.04498339295627</v>
+        <v>2.119809801355395</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
